--- a/uranai/data/ラッキースポット管理.xlsx
+++ b/uranai/data/ラッキースポット管理.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="653" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラッキースポット入力" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="マスタ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使い方_必読" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="候補リスト_リサーチ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配信ログ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="過去記事抽出_2026-05-04" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラッキースポット入力_old_2026-05-07" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ラッキースポット入力" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="マスタ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="使い方_必読" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="候補リスト_リサーチ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="配信ログ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="過去記事抽出_2026-05-04" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ラッキースポット入力_old_2026-05-07" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -858,7 +858,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>焼肉ホルモン ざくろ</t>
+          <t>キッチンながた</t>
         </is>
       </c>
     </row>
@@ -1050,6 +1050,11 @@
     <row r="34">
       <c r="A34" s="44" t="n">
         <v>46181</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>焼肉ホルモン ざくろ</t>
+        </is>
       </c>
     </row>
     <row r="35">

--- a/uranai/data/ラッキースポット管理.xlsx
+++ b/uranai/data/ラッキースポット管理.xlsx
@@ -826,11 +826,6 @@
       <c r="A12" s="44" t="n">
         <v>46159</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="44" t="n">
@@ -965,11 +960,6 @@
     <row r="26">
       <c r="A26" s="44" t="n">
         <v>46173</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
       </c>
     </row>
     <row r="27">

--- a/uranai/data/ラッキースポット管理.xlsx
+++ b/uranai/data/ラッキースポット管理.xlsx
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C240"/>
+  <dimension ref="A1:E240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1051,26 +1051,51 @@
       <c r="A35" s="44" t="n">
         <v>46182</v>
       </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BamBoo's</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="44" t="n">
         <v>46183</v>
       </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>大衆食堂くろしお</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="44" t="n">
         <v>46184</v>
       </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>手打そば つれづれ</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="44" t="n">
         <v>46185</v>
       </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>麺屋しずる</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="44" t="n">
         <v>46186</v>
       </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Fork Walks</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="44" t="n">
@@ -1091,6 +1116,11 @@
       <c r="A43" s="44" t="n">
         <v>46190</v>
       </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>うどん ひこよし</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="44" t="n">
@@ -1135,6 +1165,11 @@
     <row r="52">
       <c r="A52" s="44" t="n">
         <v>46199</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>らぁめん楓鹿</t>
+        </is>
       </c>
     </row>
     <row r="53">

--- a/uranai/data/ラッキースポット管理.xlsx
+++ b/uranai/data/ラッキースポット管理.xlsx
@@ -1106,11 +1106,21 @@
       <c r="A41" s="44" t="n">
         <v>46188</v>
       </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PISOLA豊川インター店</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="44" t="n">
         <v>46189</v>
       </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>室内ゴルフ練習場７８</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="44" t="n">
@@ -1126,15 +1136,30 @@
       <c r="A44" s="44" t="n">
         <v>46191</v>
       </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ひつまぶし専門店 長楽</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="44" t="n">
         <v>46192</v>
       </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>菓子店MONE</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="44" t="n">
         <v>46193</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CUSTARD BOYA</t>
+        </is>
       </c>
     </row>
     <row r="47">

--- a/uranai/data/ラッキースポット管理.xlsx
+++ b/uranai/data/ラッキースポット管理.xlsx
@@ -1171,21 +1171,41 @@
       <c r="A48" s="44" t="n">
         <v>46195</v>
       </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ヤギ NHAT NHAT レストラン</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="44" t="n">
         <v>46196</v>
       </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>蕎麦しずく</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="44" t="n">
         <v>46197</v>
       </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>焼肉 牛若丸</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="44" t="n">
         <v>46198</v>
       </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>インド料理ガンジス川 豊川店</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="44" t="n">
@@ -1200,6 +1220,11 @@
     <row r="53">
       <c r="A53" s="44" t="n">
         <v>46200</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>雅薫ル</t>
+        </is>
       </c>
     </row>
     <row r="54">

--- a/uranai/data/ラッキースポット管理.xlsx
+++ b/uranai/data/ラッキースポット管理.xlsx
@@ -1236,31 +1236,71 @@
       <c r="A55" s="44" t="n">
         <v>46202</v>
       </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>業務スーパー</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="44" t="n">
         <v>46203</v>
       </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>querofune</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="44" t="n">
         <v>46204</v>
       </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>無印良品</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="44" t="n">
         <v>46205</v>
       </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ブーランジュリーヨシオカ</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="44" t="n">
         <v>46206</v>
       </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Lavie et Beauty</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="44" t="n">
         <v>46207</v>
       </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>買取大吉</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="44" t="n">
@@ -1270,6 +1310,11 @@
     <row r="62">
       <c r="A62" s="44" t="n">
         <v>46209</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ブーランジェリーあまざき</t>
+        </is>
       </c>
     </row>
     <row r="63">

--- a/uranai/data/ラッキースポット管理.xlsx
+++ b/uranai/data/ラッキースポット管理.xlsx
@@ -1321,25 +1321,60 @@
       <c r="A63" s="44" t="n">
         <v>46210</v>
       </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>JUNKPOT</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="44" t="n">
         <v>46211</v>
       </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>優愛豚（ゆうあいぽーく）</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="44" t="n">
         <v>46212</v>
       </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ドラッグストアコスモス</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="44" t="n">
         <v>46213</v>
       </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>UNLAST（アンラスト）</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="44" t="n">
         <v>46214</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>のびっこジャンボ</t>
+        </is>
       </c>
     </row>
     <row r="68">

--- a/uranai/data/ラッキースポット管理.xlsx
+++ b/uranai/data/ラッキースポット管理.xlsx
@@ -1386,31 +1386,66 @@
       <c r="A69" s="44" t="n">
         <v>46216</v>
       </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Pièreposer（ピエルポゼ）</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="44" t="n">
         <v>46217</v>
       </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>HOANGNAM FOODS</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="44" t="n">
         <v>46218</v>
       </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>ミスタードーナツ</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="44" t="n">
         <v>46219</v>
       </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>串カツ田中　豊川稲荷店</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="44" t="n">
         <v>46220</v>
       </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ラーメン・餃子　北国</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="44" t="n">
         <v>46221</v>
       </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>icic shaved ice</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="44" t="n">
@@ -1445,6 +1480,11 @@
     <row r="81">
       <c r="A81" s="44" t="n">
         <v>46228</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Mecci Tart（メッチタルト）</t>
+        </is>
       </c>
     </row>
     <row r="82">

--- a/uranai/data/ラッキースポット管理.xlsx
+++ b/uranai/data/ラッキースポット管理.xlsx
@@ -1456,25 +1456,50 @@
       <c r="A76" s="44" t="n">
         <v>46223</v>
       </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>まちスマ豊川店</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="44" t="n">
         <v>46224</v>
       </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>開運ボウル</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="44" t="n">
         <v>46225</v>
       </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>田舎料理 吉野</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="44" t="n">
         <v>46226</v>
       </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>フレンチレストラン Ａｔｍｏｓ</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="44" t="n">
         <v>46227</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>鉄板バル ムライヤ ·</t>
+        </is>
       </c>
     </row>
     <row r="81">

--- a/uranai/data/ラッキースポット管理.xlsx
+++ b/uranai/data/ラッキースポット管理.xlsx
@@ -1521,30 +1521,60 @@
       <c r="A83" s="44" t="n">
         <v>46230</v>
       </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>カーゴシゴシ</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="44" t="n">
         <v>46231</v>
       </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>寺そば 萩山 慈恩寺</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="44" t="n">
         <v>46232</v>
       </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>中華楼</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="44" t="n">
         <v>46233</v>
       </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ゼッテリア</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="44" t="n">
         <v>46234</v>
       </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>イチトサンブンノイチ</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="44" t="n">
         <v>46235</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ハイジ豊川一宮店</t>
+        </is>
       </c>
     </row>
     <row r="89">

--- a/uranai/data/ラッキースポット管理.xlsx
+++ b/uranai/data/ラッキースポット管理.xlsx
@@ -1586,30 +1586,65 @@
       <c r="A90" s="44" t="n">
         <v>46237</v>
       </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>牛角焼肉食堂</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="44" t="n">
         <v>46238</v>
       </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>kiRaku（キラク）</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="44" t="n">
         <v>46239</v>
       </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ミラフィットネス豊川一宮店</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="44" t="n">
         <v>46240</v>
       </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ゲンキー</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="44" t="n">
         <v>46241</v>
       </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>syndi．豊川店</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="44" t="n">
         <v>46242</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>おりがみ農園</t>
+        </is>
       </c>
     </row>
     <row r="96">

--- a/uranai/data/ラッキースポット管理.xlsx
+++ b/uranai/data/ラッキースポット管理.xlsx
@@ -1656,30 +1656,65 @@
       <c r="A97" s="44" t="n">
         <v>46244</v>
       </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>門前テラス縁福</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="44" t="n">
         <v>46245</v>
       </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>喫茶室イノマ</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="44" t="n">
         <v>46246</v>
       </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>中国料理 清龍</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="44" t="n">
         <v>46247</v>
       </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>スパゲッ亭チャオ</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="44" t="n">
         <v>46248</v>
       </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>門前横丁</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="44" t="n">
         <v>46249</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>焼豚ラーメン 弥太郎</t>
+        </is>
       </c>
     </row>
     <row r="103">

--- a/uranai/data/ラッキースポット管理.xlsx
+++ b/uranai/data/ラッキースポット管理.xlsx
@@ -1726,30 +1726,70 @@
       <c r="A104" s="44" t="n">
         <v>46251</v>
       </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>ドクターストレッチ</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="44" t="n">
         <v>46252</v>
       </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>ダイソー</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="44" t="n">
         <v>46253</v>
       </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>赤虎</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="44" t="n">
         <v>46254</v>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>アエナ</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="44" t="n">
         <v>46255</v>
       </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>ＦＩＴ－ＥＡＳＹ</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="44" t="n">
         <v>46256</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Ｐｉｎｏ Ｂｌａｎｃ 豊川店</t>
+        </is>
       </c>
     </row>
     <row r="110">

--- a/uranai/data/ラッキースポット管理.xlsx
+++ b/uranai/data/ラッキースポット管理.xlsx
@@ -1801,30 +1801,60 @@
       <c r="A111" s="44" t="n">
         <v>46258</v>
       </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>粋 〜ＩＫＩ〜</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="44" t="n">
         <v>46259</v>
       </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>蒙古タンメン中本</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="44" t="n">
         <v>46260</v>
       </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>ホワイトニングショップ豊川店</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="44" t="n">
         <v>46261</v>
       </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>魚多花　ＵＴＡＧＥ</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="44" t="n">
         <v>46262</v>
       </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>シャンパンハウス</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="44" t="n">
         <v>46263</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>喫茶コトリ小屋</t>
+        </is>
       </c>
     </row>
     <row r="117">

--- a/uranai/data/ラッキースポット管理.xlsx
+++ b/uranai/data/ラッキースポット管理.xlsx
@@ -1866,30 +1866,60 @@
       <c r="A118" s="44" t="n">
         <v>46265</v>
       </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>ｃａｆｅ  ｂｌｕ</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="44" t="n">
         <v>46266</v>
       </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>マシンピラティス専門店 Ｓｗａｎ豊川店</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="44" t="n">
         <v>46267</v>
       </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>食堂ＣＡＦＥ　まんざいらく</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="44" t="n">
         <v>46268</v>
       </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>`olu`olu elua</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="44" t="n">
         <v>46269</v>
       </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>健の台所（健 為当店）</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="44" t="n">
         <v>46270</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>米粉パン えがおのたね</t>
+        </is>
       </c>
     </row>
     <row r="124">

--- a/uranai/data/ラッキースポット管理.xlsx
+++ b/uranai/data/ラッキースポット管理.xlsx
@@ -1931,30 +1931,60 @@
       <c r="A125" s="44" t="n">
         <v>46272</v>
       </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>茶房 遊菴</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="44" t="n">
         <v>46273</v>
       </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>からあげ カラコ</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="44" t="n">
         <v>46274</v>
       </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>ハイボール酒場 水屋</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="44" t="n">
         <v>46275</v>
       </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>長谷川餃子</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="44" t="n">
         <v>46276</v>
       </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>あらびか</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="44" t="n">
         <v>46277</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>お好み焼き うめ</t>
+        </is>
       </c>
     </row>
     <row r="131">
